--- a/VerveStacks_DEU_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DEU_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15FFE9B3-918C-4F96-A620-11991140E581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{995379CF-EA4F-4704-8CF4-3FE23145B6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{93774C28-BA0D-4B0A-A7B5-9A63157E6CCB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3F1F7E8E-38C4-4420-AEA9-31BADD683DFC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3850,7 +3850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E670DD8-F1A7-4E51-9092-D57153627007}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D924F2-1818-4A95-8228-2A2A88ED65D0}">
   <dimension ref="B3:L561"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DEU_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DEU_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{995379CF-EA4F-4704-8CF4-3FE23145B6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3A67C00-306E-4A3A-91C7-0BE85CEAB68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3F1F7E8E-38C4-4420-AEA9-31BADD683DFC}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{DE1345CD-583E-432F-90A5-5B0EE3BA9D64}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3850,7 +3850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D924F2-1818-4A95-8228-2A2A88ED65D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E49E25-6131-48CA-A004-868F0E41628C}">
   <dimension ref="B3:L561"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DEU_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DEU_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3A67C00-306E-4A3A-91C7-0BE85CEAB68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B621915D-F193-4DCC-BF36-9B832B125D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{DE1345CD-583E-432F-90A5-5B0EE3BA9D64}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1B600DE9-0011-4352-9F90-F8000F0DFA01}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3850,7 +3850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E49E25-6131-48CA-A004-868F0E41628C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A2AD0F-3E39-4F49-BD45-387263E656CE}">
   <dimension ref="B3:L561"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
